--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512409_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512409_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9227</v>
+        <v>4.4576</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4327</v>
+        <v>3.646</v>
       </c>
       <c r="F2" t="n">
-        <v>1.49</v>
+        <v>0.8116</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.0448</v>
+        <v>-1.0747</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9367</v>
+        <v>-0.9482</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1081</v>
+        <v>-0.1265</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2997</v>
+        <v>-0.2774</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3787</v>
+        <v>-0.3569</v>
       </c>
       <c r="L2" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7451</v>
+        <v>-0.7973</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5913</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1871</v>
+        <v>-0.206</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5237</v>
+        <v>1.0469</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9113</v>
+        <v>0.0534</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6124</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>4.4438</v>
+        <v>4.4855</v>
       </c>
       <c r="W2" t="n">
-        <v>4.0259</v>
+        <v>4.0725</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4179</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8804</v>
+        <v>2.6071</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2865</v>
+        <v>2.4004</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5939</v>
+        <v>0.2068</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0975</v>
+        <v>2.2866</v>
       </c>
       <c r="H3" t="n">
-        <v>1.503</v>
+        <v>3.5559</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4055</v>
+        <v>-1.2693</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7687</v>
+        <v>3.0461</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7542</v>
+        <v>4.5423</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0145</v>
+        <v>-1.4962</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6712</v>
+        <v>-0.7595</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2512</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.42</v>
+        <v>0.2269</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8194</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8436</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9635</v>
+        <v>0.0614</v>
       </c>
       <c r="T3" t="n">
-        <v>0.542</v>
+        <v>-0.2286</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4215</v>
+        <v>0.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6639</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5951</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9946</v>
+        <v>2.4346</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2664</v>
+        <v>1.9757</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7282</v>
+        <v>0.4588</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4335</v>
+        <v>3.4253</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8919</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5415</v>
+        <v>2.5356</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5192</v>
+        <v>2.5556</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2548</v>
+        <v>1.2834</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2645</v>
+        <v>1.2722</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9142</v>
+        <v>0.8697</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3628</v>
+        <v>-0.3938</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2771</v>
+        <v>1.2635</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7004</v>
+        <v>-0.2257</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.048</v>
+        <v>-0.3774</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3476</v>
+        <v>0.1516</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.353</v>
+        <v>-1.3723</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.353</v>
+        <v>-1.3723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9096</v>
+        <v>2.4164</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0223</v>
+        <v>1.0913</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1128</v>
+        <v>1.3251</v>
       </c>
       <c r="G5" t="n">
-        <v>2.244</v>
+        <v>1.116</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5127</v>
+        <v>1.54</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2687</v>
+        <v>-0.4239</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9385</v>
+        <v>1.839</v>
       </c>
       <c r="K5" t="n">
-        <v>4.461</v>
+        <v>1.8155</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.5225</v>
+        <v>0.0235</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6944</v>
+        <v>-0.7229</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9483</v>
+        <v>-0.2755</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2539</v>
+        <v>-0.4474</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4097</v>
+        <v>0.8098</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6145</v>
+        <v>1.8221</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5847</v>
+        <v>0.4906</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4822</v>
+        <v>0.2646</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1025</v>
+        <v>0.226</v>
       </c>
       <c r="V5" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5903</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5037</v>
+        <v>1.9303</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0711</v>
+        <v>1.4778</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4327</v>
+        <v>0.4525</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3594</v>
+        <v>0.3347</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7388</v>
+        <v>-0.7506</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0982</v>
+        <v>1.0853</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8355</v>
+        <v>0.8601</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1008</v>
+        <v>-1.0879</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9362</v>
+        <v>1.948</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4761</v>
+        <v>-0.5254</v>
       </c>
       <c r="N6" t="n">
-        <v>0.362</v>
+        <v>0.3373</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.838</v>
+        <v>-0.8627</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0215</v>
+        <v>0.4741</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2857</v>
+        <v>0.0673</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3072</v>
+        <v>0.4068</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1062</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7262</v>
+        <v>0.7528</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8324</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5087</v>
+        <v>0.8467</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6274</v>
+        <v>2.214</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1361</v>
+        <v>-1.3673</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2011</v>
+        <v>0.8589</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4403</v>
+        <v>1.6981</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2392</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5792</v>
+        <v>3.2489</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0781</v>
+        <v>2.0328</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6572</v>
+        <v>1.2161</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7803</v>
+        <v>-2.39</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3623</v>
+        <v>-0.3346</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4181</v>
+        <v>-2.0553</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.4049</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2048</v>
+        <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2048</v>
+        <v>1.4172</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0655</v>
+        <v>0.5221</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3275</v>
+        <v>-0.2736</v>
       </c>
       <c r="U7" t="n">
-        <v>0.393</v>
+        <v>0.7957</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2421</v>
+        <v>-0.9393</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4841</v>
+        <v>0.2509</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2421</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1159</v>
+        <v>0.7847</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4042</v>
+        <v>-0.3224</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2883</v>
+        <v>1.1071</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8383</v>
+        <v>0.1981</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6618</v>
+        <v>0.4351</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8235</v>
+        <v>-0.2371</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1688</v>
+        <v>-0.5733</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9689</v>
+        <v>0.079</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>-0.6523</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3305</v>
+        <v>0.7714</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.307</v>
+        <v>0.3561</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0235</v>
+        <v>0.4153</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4097</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>-0.2025</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4339</v>
+        <v>0.2025</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1936</v>
+        <v>0.3357</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9825</v>
+        <v>-0.0485</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7889</v>
+        <v>0.3842</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9385</v>
+        <v>0.2509</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2421</v>
+        <v>0.5019</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1806</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2356</v>
+        <v>-1.5509</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3901</v>
+        <v>-3.7427</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1545</v>
+        <v>2.1917</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8297</v>
+        <v>-1.8335</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.794</v>
+        <v>-0.772</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0356</v>
+        <v>-1.0615</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7662</v>
+        <v>-1.6833</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5702</v>
+        <v>-0.4979</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1959</v>
+        <v>-1.1854</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0635</v>
+        <v>-0.1502</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2238</v>
+        <v>-0.2742</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1603</v>
+        <v>0.1239</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8969</v>
+        <v>0.5702</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3873</v>
+        <v>-0.0834</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5095</v>
+        <v>0.6535</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3117</v>
+        <v>0.3198</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0696</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4902</v>
+        <v>-1.6278</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8137</v>
+        <v>-1.0491</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6765</v>
+        <v>-0.5787</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3578</v>
+        <v>-3.3475</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.5451</v>
+        <v>-3.5199</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1873</v>
+        <v>0.1724</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4728</v>
+        <v>-1.3741</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.5687</v>
+        <v>-2.4945</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0959</v>
+        <v>1.1204</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.885</v>
+        <v>-1.9734</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-1.0254</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9087</v>
+        <v>-0.948</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7848000000000001</v>
+        <v>0.0398</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8752</v>
+        <v>-0.2616</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.3014</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0379</v>
+        <v>1.0726</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5585</v>
+        <v>1.5988</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.5263</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1814</v>
+        <v>-3.3599</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1234</v>
+        <v>-1.2257</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.058</v>
+        <v>-2.1341</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.924</v>
+        <v>-1.9244</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1566</v>
+        <v>-1.147</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7674</v>
+        <v>-0.7774</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7105</v>
+        <v>-0.6928</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7105</v>
+        <v>-0.6928</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2135</v>
+        <v>-1.2316</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4461</v>
+        <v>-0.4542</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7674</v>
+        <v>-0.7774</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.3621</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3693</v>
+        <v>0.2283</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1685</v>
+        <v>0.1337</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.9284</v>
+        <v>8.938800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.528599999999999</v>
+        <v>6.4653</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3998</v>
+        <v>2.4735</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01749999999999963</v>
+        <v>0.03949999999999965</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8385000000000002</v>
+        <v>0.9810000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8210000000000001</v>
+        <v>-0.9416000000000004</v>
       </c>
       <c r="J12" t="n">
-        <v>6.402299999999999</v>
+        <v>6.9488</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1881</v>
+        <v>4.622999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>2.2145</v>
+        <v>2.3258</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.384799999999999</v>
+        <v>-6.9092</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.3492</v>
+        <v>-3.642</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.0353</v>
+        <v>-3.2672</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.1935</v>
+        <v>-8.0985</v>
       </c>
       <c r="R12" t="n">
-        <v>10.2422</v>
+        <v>10.1228</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7454</v>
+        <v>3.6772</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7912</v>
+        <v>-0.6595000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>4.5364</v>
+        <v>4.3363</v>
       </c>
       <c r="V12" t="n">
-        <v>3.1172</v>
+        <v>3.1977</v>
       </c>
       <c r="W12" t="n">
-        <v>8.1113</v>
+        <v>8.2738</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.994400000000001</v>
+        <v>-5.0762</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.334</v>
+        <v>5.0405</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7187</v>
+        <v>5.2075</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3847</v>
+        <v>-0.167</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9186</v>
+        <v>2.9303</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5672</v>
+        <v>2.5696</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3514</v>
+        <v>0.3607</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3979</v>
+        <v>3.4448</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7907</v>
+        <v>2.825</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6072</v>
+        <v>0.6198</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4793</v>
+        <v>-0.5145</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2235</v>
+        <v>-0.2553</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2558</v>
+        <v>-0.2591</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7652</v>
+        <v>-0.08</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4501</v>
+        <v>-0.0226</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3151</v>
+        <v>-0.0574</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0458</v>
+        <v>3.522</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6858</v>
+        <v>3.4951</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3599</v>
+        <v>0.0269</v>
       </c>
       <c r="G14" t="n">
-        <v>5.9892</v>
+        <v>6.0328</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8571</v>
+        <v>2.8658</v>
       </c>
       <c r="I14" t="n">
-        <v>3.132</v>
+        <v>3.167</v>
       </c>
       <c r="J14" t="n">
-        <v>6.0884</v>
+        <v>6.1948</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6071</v>
+        <v>2.6656</v>
       </c>
       <c r="L14" t="n">
-        <v>3.4814</v>
+        <v>3.5292</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0993</v>
+        <v>-0.1619</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2501</v>
+        <v>0.2002</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3493</v>
+        <v>-0.3621</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.663</v>
+        <v>-2.6319</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8707</v>
+        <v>-0.4741</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1622</v>
+        <v>-0.509</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2916</v>
+        <v>0.0349</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9896</v>
+        <v>0.8663</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5037</v>
+        <v>1.6493</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5141</v>
+        <v>-0.783</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1114</v>
+        <v>0.8343</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6272</v>
+        <v>-0.4939</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5158</v>
+        <v>1.3282</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6008</v>
+        <v>2.0232</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.125</v>
+        <v>0.592</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7258</v>
+        <v>1.4312</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-1.1889</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5022</v>
+        <v>-1.0859</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.21</v>
+        <v>-0.103</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8194</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8194</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.356</v>
+        <v>-0.5753</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3127</v>
+        <v>-0.3738</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0434</v>
+        <v>-0.2015</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0744</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5903</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.697</v>
+        <v>0.2491</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6096</v>
+        <v>-0.7883</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9126</v>
+        <v>1.0374</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8411</v>
+        <v>-0.2379</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4879</v>
+        <v>-0.157</v>
       </c>
       <c r="I16" t="n">
-        <v>1.329</v>
+        <v>-0.081</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9943</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5717</v>
+        <v>-0.5736</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4225</v>
+        <v>0.0398</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1531</v>
+        <v>0.2959</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0596</v>
+        <v>0.4166</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0935</v>
+        <v>-0.1207</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6145</v>
+        <v>0.4049</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6145</v>
+        <v>0.4049</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7586000000000001</v>
+        <v>0.3331</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3846</v>
+        <v>-0.2545</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.374</v>
+        <v>0.5876</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0426</v>
+        <v>-0.1675</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0591</v>
+        <v>1.4104</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0165</v>
+        <v>-1.5779</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1445</v>
+        <v>-0.1169</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5434</v>
+        <v>-0.6323</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6011</v>
+        <v>0.5154</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8241</v>
+        <v>0.639</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5475</v>
+        <v>-0.1001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2766</v>
+        <v>0.7391</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6796</v>
+        <v>-0.7559</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0041</v>
+        <v>-0.5322</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3245</v>
+        <v>-0.2237</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0917</v>
+        <v>0.2366</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.007</v>
+        <v>0.1763</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0987</v>
+        <v>0.0603</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.013</v>
+        <v>-1.097</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2421</v>
+        <v>0.5951</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.255</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0399</v>
+        <v>-0.2857</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1213</v>
+        <v>-0.0733</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1612</v>
+        <v>-0.2124</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2111</v>
+        <v>-0.5946</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1342</v>
+        <v>-0.2368</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0769</v>
+        <v>-0.3578</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5402</v>
+        <v>0.1188</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5797</v>
+        <v>0.079</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3291</v>
+        <v>-0.7134</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4455</v>
+        <v>-0.3158</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1164</v>
+        <v>-0.3975</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0833</v>
+        <v>-0.096</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.1921</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6645</v>
+        <v>0.096</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.025</v>
+        <v>-0.3365</v>
       </c>
       <c r="E19" t="n">
-        <v>0.977</v>
+        <v>0.7965</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.952</v>
+        <v>-1.133</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5193</v>
+        <v>-0.5545</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4632</v>
+        <v>-0.4927</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0561</v>
+        <v>-0.0618</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7503</v>
+        <v>0.7551</v>
       </c>
       <c r="K19" t="n">
-        <v>0.039</v>
+        <v>0.0395</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7113</v>
+        <v>0.7156</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2696</v>
+        <v>-1.3096</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5022</v>
+        <v>-0.5322</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7674</v>
+        <v>-0.7774</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0702</v>
+        <v>-0.3894</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0154</v>
+        <v>-0.2095</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0549</v>
+        <v>-0.1798</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3318</v>
+        <v>-0.3811</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0789</v>
+        <v>1.806</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2529</v>
+        <v>-2.1871</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5843</v>
+        <v>1.1247</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2287</v>
+        <v>0.5342</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3556</v>
+        <v>0.5905</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1176</v>
+        <v>1.858</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0781</v>
+        <v>1.5797</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>0.2783</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7019</v>
+        <v>-0.7333</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3068</v>
+        <v>-1.0455</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3952</v>
+        <v>0.3122</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4097</v>
+        <v>0.8098</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4097</v>
+        <v>0.8098</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1572</v>
+        <v>-0.2794</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1965</v>
+        <v>-0.303</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0393</v>
+        <v>0.0236</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.0362</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.2872</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4393</v>
+        <v>-1.4196</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5767</v>
+        <v>-2.4593</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1374</v>
+        <v>1.0397</v>
       </c>
       <c r="G21" t="n">
-        <v>0.245</v>
+        <v>0.2588</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1794</v>
+        <v>-1.2045</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4245</v>
+        <v>1.4634</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5114</v>
+        <v>0.5793</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9837</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4951</v>
+        <v>1.5487</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2664</v>
+        <v>-0.3205</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1957</v>
+        <v>-0.2352</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0706</v>
+        <v>-0.0853</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6229</v>
+        <v>-0.6177</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0396</v>
+        <v>-1.0142</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4167</v>
+        <v>0.3965</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5203</v>
+        <v>-3.3582</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9347</v>
+        <v>-2.3684</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5856</v>
+        <v>-0.9898</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2108</v>
+        <v>-0.1755</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1191</v>
+        <v>3.123</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3299</v>
+        <v>-3.2985</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3345</v>
+        <v>-0.2313</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6461</v>
+        <v>2.7051</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.9806</v>
+        <v>-2.9364</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1236</v>
+        <v>0.0558</v>
       </c>
       <c r="N22" t="n">
-        <v>0.473</v>
+        <v>0.4179</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3493</v>
+        <v>-0.3621</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.358</v>
+        <v>-0.2072</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2277</v>
+        <v>-0.7806</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8698</v>
+        <v>0.5735</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.9515</v>
+        <v>-2.9755</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.6033</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5492</v>
+        <v>-4.3107</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2558</v>
+        <v>-4.9374</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7067</v>
+        <v>0.6267</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.0624</v>
+        <v>-4.0696</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3278</v>
+        <v>-2.3511</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7346</v>
+        <v>-1.7185</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.3322</v>
+        <v>-3.2984</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2959</v>
+        <v>-1.2854</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0362</v>
+        <v>-2.013</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7302</v>
+        <v>-0.7712</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0318</v>
+        <v>-1.0657</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3016</v>
+        <v>0.2945</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.4582</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1477</v>
+        <v>0.0589</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.2943</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3679</v>
+        <v>0.3531</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1191</v>
+        <v>2.1295</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6647</v>
+        <v>1.6921</v>
       </c>
       <c r="X23" t="n">
-        <v>0.4544</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2616</v>
+        <v>-7.3969</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.9864</v>
+        <v>-6.2115</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2752</v>
+        <v>-1.1854</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.4566</v>
+        <v>-5.4715</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.4769</v>
+        <v>-4.5055</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9797</v>
+        <v>-0.966</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.6931</v>
+        <v>-4.6401</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.9464</v>
+        <v>-3.9155</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7468</v>
+        <v>-0.7246</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7634</v>
+        <v>-0.8314</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5305</v>
+        <v>-0.59</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2329</v>
+        <v>-0.2414</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5258</v>
+        <v>-0.6259</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.269</v>
+        <v>-0.5591</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2568</v>
+        <v>-0.0668</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0744</v>
+        <v>-1.097</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0744</v>
+        <v>-1.097</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.9283</v>
+        <v>-7.9783</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.399899999999998</v>
+        <v>-2.473399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.5284</v>
+        <v>-5.504899999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.01750000000000185</v>
+        <v>-0.0395999999999983</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8384999999999989</v>
+        <v>-0.9811999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.821</v>
+        <v>0.9415999999999998</v>
       </c>
       <c r="J25" t="n">
-        <v>6.384799999999999</v>
+        <v>6.909400000000002</v>
       </c>
       <c r="K25" t="n">
-        <v>3.349500000000001</v>
+        <v>3.642</v>
       </c>
       <c r="L25" t="n">
-        <v>3.0353</v>
+        <v>3.2675</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.4023</v>
+        <v>-6.948900000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.1878</v>
+        <v>-4.6231</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.2143</v>
+        <v>-2.3256</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q25" t="n">
-        <v>-10.2423</v>
+        <v>-10.1227</v>
       </c>
       <c r="R25" t="n">
-        <v>8.1938</v>
+        <v>8.098199999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.7453</v>
+        <v>-2.7164</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.5361</v>
+        <v>-4.336399999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7911</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.1172</v>
+        <v>-3.1976</v>
       </c>
       <c r="W25" t="n">
-        <v>4.9943</v>
+        <v>5.0761</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.111400000000001</v>
+        <v>-8.2738</v>
       </c>
     </row>
   </sheetData>
